--- a/data/trans_camb/IP07_R-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/IP07_R-Estudios-trans_camb.xlsx
@@ -529,14 +529,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -624,32 +624,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>1,77</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>13,43</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>2,47</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>-10,95</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>1,67</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>-9,09</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>1,77</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>13,43</t>
-        </is>
-      </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,7</t>
+          <t>-3,75</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>-2,72</t>
+          <t>-0,92</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-21,01; -0,93</t>
+          <t>-9,85; 13,33</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-10,07; 11,56</t>
+          <t>1,11; 24,86</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-32,11; 4,97</t>
+          <t>-10,95; 15,62</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-8,95; 13,26</t>
+          <t>-21,11; 0,1</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,66; 24,01</t>
+          <t>-9,9; 11,59</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-10,17; 15,95</t>
+          <t>-16,9; 8,43</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-12,75; 3,13</t>
+          <t>-12,23; 2,59</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-1,52; 14,46</t>
+          <t>0,29; 15,54</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-16,32; 6,72</t>
+          <t>-10,63; 8,16</t>
         </is>
       </c>
     </row>
@@ -730,32 +730,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>2,58%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>19,58%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>3,61%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>-14,02%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>2,14%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>-11,64%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>2,58%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>19,58%</t>
-        </is>
-      </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>5,4%</t>
+          <t>-4,8%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>-3,7%</t>
+          <t>-1,26%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-25,47; -1,15</t>
+          <t>-13,15; 21,54</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-12,56; 15,74</t>
+          <t>1,63; 40,67</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-41,2; 6,45</t>
+          <t>-14,62; 24,43</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-12,22; 21,53</t>
+          <t>-26,03; -0,09</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1,38; 38,23</t>
+          <t>-12,15; 15,77</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-13,68; 25,68</t>
+          <t>-21,56; 11,1</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-16,35; 4,29</t>
+          <t>-15,89; 3,74</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-1,84; 20,75</t>
+          <t>0,16; 22,09</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-21,24; 9,38</t>
+          <t>-14,37; 11,69</t>
         </is>
       </c>
     </row>
@@ -840,32 +840,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>-1,28</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>10,45</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>0,26</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>-0,16</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>11,55</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>2,37</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>-1,28</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>10,45</t>
-        </is>
-      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0,73</t>
+          <t>0,85</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>1,51</t>
+          <t>0,55</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-4,43; 4,47</t>
+          <t>-6,23; 3,19</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>7,27; 15,83</t>
+          <t>6,17; 14,66</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-2,65; 7,89</t>
+          <t>-5,37; 5,45</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-5,84; 2,9</t>
+          <t>-4,55; 4,28</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>6,59; 14,62</t>
+          <t>7,32; 16,02</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-4,92; 5,93</t>
+          <t>-3,63; 6,08</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-4,32; 2,16</t>
+          <t>-3,84; 2,62</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>8,39; 14,05</t>
+          <t>8,23; 13,88</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-2,27; 5,36</t>
+          <t>-3,08; 3,97</t>
         </is>
       </c>
     </row>
@@ -946,32 +946,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>-1,69%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>13,78%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>0,34%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>-0,2%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>15,0%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>3,08%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>-1,69%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>13,78%</t>
-        </is>
-      </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>0,72%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-5,64; 6,01</t>
+          <t>-7,95; 4,27</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>9,08; 21,32</t>
+          <t>7,85; 20,09</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-3,38; 10,62</t>
+          <t>-6,96; 7,32</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-7,54; 3,94</t>
+          <t>-5,72; 5,69</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>8,32; 19,81</t>
+          <t>9,31; 21,58</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-6,41; 8,02</t>
+          <t>-4,57; 8,12</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-5,53; 2,88</t>
+          <t>-4,9; 3,52</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>10,77; 19,0</t>
+          <t>10,55; 18,64</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-2,89; 7,16</t>
+          <t>-3,98; 5,32</t>
         </is>
       </c>
     </row>
@@ -1056,32 +1056,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>-6,28</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>2,78</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>-7,3</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>-3,34</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>7,28</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>-5,08</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>-6,28</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>2,78</t>
-        </is>
-      </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-7,58</t>
+          <t>-5,86</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>-6,11</t>
+          <t>-6,37</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-10,49; 4,56</t>
+          <t>-13,24; 0,64</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,93; 13,95</t>
+          <t>-3,89; 9,0</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-12,61; 2,38</t>
+          <t>-14,47; 0,5</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-13,57; 1,2</t>
+          <t>-10,43; 4,17</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-3,11; 9,1</t>
+          <t>0,79; 13,63</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-15,28; -0,02</t>
+          <t>-14,24; 0,86</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-9,92; 0,54</t>
+          <t>-10,28; 0,55</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,68; 9,65</t>
+          <t>0,68; 9,62</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-11,94; -0,68</t>
+          <t>-11,8; -1,17</t>
         </is>
       </c>
     </row>
@@ -1162,32 +1162,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>-7,52%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>3,33%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>-8,74%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>-4,24%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>9,24%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>-6,45%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>-7,52%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>3,33%</t>
-        </is>
-      </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>-9,08%</t>
+          <t>-7,44%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>-7,54%</t>
+          <t>-7,86%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-12,99; 6,2</t>
+          <t>-15,5; 0,74</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1,16; 18,72</t>
+          <t>-4,55; 11,22</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-15,37; 3,2</t>
+          <t>-16,8; 0,62</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-15,84; 1,35</t>
+          <t>-12,67; 5,53</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-3,53; 11,37</t>
+          <t>0,98; 18,11</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-18,27; -0,07</t>
+          <t>-17,69; 1,28</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-11,95; 0,74</t>
+          <t>-12,21; 0,33</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0,87; 12,55</t>
+          <t>0,86; 12,27</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-14,31; -0,83</t>
+          <t>-14,17; -1,49</t>
         </is>
       </c>
     </row>
@@ -1272,32 +1272,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>-1,96</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>9,25</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>-0,93</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>-2,35</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>9,59</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>-0,36</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>-1,96</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>9,25</t>
-        </is>
-      </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-0,58</t>
+          <t>-1,19</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>-0,5</t>
+          <t>-1,07</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-5,69; 1,33</t>
+          <t>-5,41; 1,96</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>6,36; 12,83</t>
+          <t>6,32; 12,77</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-4,44; 3,92</t>
+          <t>-5,11; 2,9</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-5,62; 1,63</t>
+          <t>-5,88; 1,71</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>6,04; 12,57</t>
+          <t>6,28; 12,78</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-5,26; 3,28</t>
+          <t>-4,97; 2,56</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-4,76; 0,62</t>
+          <t>-4,78; 0,43</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>7,05; 11,67</t>
+          <t>6,97; 11,63</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-3,58; 2,57</t>
+          <t>-4,03; 1,7</t>
         </is>
       </c>
     </row>
@@ -1378,32 +1378,32 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>-2,55%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>12,06%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>-1,21%</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
           <t>-3,03%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>12,36%</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>-0,47%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>-2,55%</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>12,06%</t>
-        </is>
-      </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-0,76%</t>
+          <t>-1,54%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>-0,65%</t>
+          <t>-1,38%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-7,19; 1,77</t>
+          <t>-6,84; 2,66</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>7,97; 16,88</t>
+          <t>8,09; 17,06</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-5,68; 5,07</t>
+          <t>-6,55; 3,89</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-7,19; 2,16</t>
+          <t>-7,47; 2,23</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>7,7; 16,86</t>
+          <t>7,94; 16,92</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-6,73; 4,35</t>
+          <t>-6,27; 3,4</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-6,14; 0,81</t>
+          <t>-6,14; 0,55</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>8,96; 15,38</t>
+          <t>8,87; 15,38</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-4,57; 3,29</t>
+          <t>-5,15; 2,22</t>
         </is>
       </c>
     </row>
